--- a/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.414277</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.752222</v>
-      </c>
-      <c r="I2" t="n">
-        <v>204</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.414277</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.752222</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>80832</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.6022</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.7216</v>
-      </c>
-      <c r="I3" t="n">
-        <v>41</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.6022</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.7216</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>218</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.414569999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.75069000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>208</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.41457</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.75069</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1588 MI MUNDO FELIZ</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.42408</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.78323</v>
-      </c>
-      <c r="I5" t="n">
-        <v>130</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.42408</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.78323</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>VIRU</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.413790000000002</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.75171</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2616</v>
-      </c>
-      <c r="J6" t="n">
-        <v>106</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.413790000000002</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.75171</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>80070 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.416539999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.75072</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1917</v>
-      </c>
-      <c r="J7" t="n">
-        <v>79</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.41654</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.75072</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>80073 JOSE ABELARDO QUIÑONEZ GONZALES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.3734</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.65430000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>252</v>
-      </c>
-      <c r="J8" t="n">
-        <v>19</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.3734</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.6543</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>80074 MARIA CARIDAD AGUERO DE ARRESSE</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.423503999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.781147</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2429</v>
-      </c>
-      <c r="J9" t="n">
-        <v>97</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.423504</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.781147</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>80075</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.427536999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.83575999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>566</v>
-      </c>
-      <c r="J10" t="n">
-        <v>31</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.427537</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.83576</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>80095 JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.44797</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.818405</v>
-      </c>
-      <c r="I11" t="n">
-        <v>410</v>
-      </c>
-      <c r="J11" t="n">
-        <v>22</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.44797</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.818405</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>80096 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.4679</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.8476</v>
-      </c>
-      <c r="I12" t="n">
-        <v>371</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.4679</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.8476</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>80702 MARIA SANDOVAL ROBLES</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.409058999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.80837</v>
-      </c>
-      <c r="I13" t="n">
-        <v>905</v>
-      </c>
-      <c r="J13" t="n">
-        <v>35</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.409059</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.80837</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>80704 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.3796</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.6795</v>
-      </c>
-      <c r="I14" t="n">
-        <v>282</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.3796</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.6795</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>81700</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.405139999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-78.82339</v>
-      </c>
-      <c r="I15" t="n">
-        <v>716</v>
-      </c>
-      <c r="J15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.40514</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.82339</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>81701</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.431685</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.797331</v>
-      </c>
-      <c r="I16" t="n">
-        <v>101</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.431685</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.797331</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>80755</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.467280000000002</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.866609</v>
-      </c>
-      <c r="I17" t="n">
-        <v>493</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.467280000000002</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.866609</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.412940000000003</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.7529</v>
-      </c>
-      <c r="I18" t="n">
-        <v>289</v>
-      </c>
-      <c r="J18" t="n">
-        <v>15</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.412940000000003</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.7529</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>80635 SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.48039</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.63298</v>
-      </c>
-      <c r="I19" t="n">
-        <v>931</v>
-      </c>
-      <c r="J19" t="n">
-        <v>42</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.48039</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.63298</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>81540</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-8.7464</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-78.52209999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>273</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-8.7464</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-78.5221</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>81770 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-8.537134999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.671621</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1877</v>
-      </c>
-      <c r="J21" t="n">
-        <v>67</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-8.537135</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.671621</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1877</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>GENERAL SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-8.42276</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-78.77880999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>35</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-8.42276</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-78.77881</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAGRADOS CORAZONES</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-8.42159</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.77616</v>
-      </c>
-      <c r="I23" t="n">
-        <v>327</v>
-      </c>
-      <c r="J23" t="n">
-        <v>11</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8.42159</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.77616</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>2109</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-8.5382</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.67400000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>87</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-8.5382</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.674</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>81700</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-8.404579999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.82329</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1140</v>
-      </c>
-      <c r="J25" t="n">
-        <v>41</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-8.40458</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.82329</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>2117</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.4053</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-78.82128</v>
-      </c>
-      <c r="I26" t="n">
-        <v>236</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.4053</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-78.82128</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-8.42394</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-78.77688000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>179</v>
-      </c>
-      <c r="J27" t="n">
-        <v>14</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-8.42394</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-78.77688</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.41512</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-78.75524</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.41512</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-78.75524</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-8.40305</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.82274</v>
-      </c>
-      <c r="I29" t="n">
-        <v>593</v>
-      </c>
-      <c r="J29" t="n">
-        <v>24</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-8.40305</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.82274</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>ADVENTURE SCHOOL'S</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-8.420669999999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.77187000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>227</v>
-      </c>
-      <c r="J30" t="n">
-        <v>13</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-8.42067</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.77187</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-8.538320000000002</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.67471</v>
-      </c>
-      <c r="I31" t="n">
-        <v>462</v>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-8.538320000000002</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.67471</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>2175</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-8.602</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-78.7218</v>
-      </c>
-      <c r="I32" t="n">
-        <v>17</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-8.602</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-78.7218</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>COAR LA LIBERTAD</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-8.410080000000002</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-78.72450000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>278</v>
-      </c>
-      <c r="J33" t="n">
-        <v>30</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-8.410080000000002</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-78.7245</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>2278</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-8.411289999999999</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-78.81253</v>
-      </c>
-      <c r="I34" t="n">
-        <v>68</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-8.41129</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-78.81253</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>2285</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-8.432449999999999</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-78.77128999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>65</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-8.43245</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-78.77129</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>CHRISTIAN BARNARD</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-8.405150000000003</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-78.82216</v>
-      </c>
-      <c r="I36" t="n">
-        <v>609</v>
-      </c>
-      <c r="J36" t="n">
-        <v>27</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-8.405150000000003</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-78.82216</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>MARIA DE FATIMA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-8.42456</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-78.77975000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>261</v>
-      </c>
-      <c r="J37" t="n">
-        <v>16</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-8.42456</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-78.77975</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-8.546137</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-78.677008</v>
-      </c>
-      <c r="I38" t="n">
-        <v>461</v>
-      </c>
-      <c r="J38" t="n">
-        <v>21</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-8.546137</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-78.677008</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-8.416169999999999</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-78.75837</v>
-      </c>
-      <c r="I39" t="n">
-        <v>470</v>
-      </c>
-      <c r="J39" t="n">
-        <v>20</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-8.41617</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-78.75837</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>82206 VALLE DE DIOS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-8.512575</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-78.68038900000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1632</v>
-      </c>
-      <c r="J40" t="n">
-        <v>62</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-8.512575</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-78.680389</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1632</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>GARDNER SCHOOL</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-8.418537000000002</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-78.765733</v>
-      </c>
-      <c r="I41" t="n">
-        <v>309</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-8.418537000000002</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-78.765733</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>80755</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-8.4663</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-78.86839999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-8.4663</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-78.8684</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>657913</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.414277</t>
+          <t>-8.41512</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.752222</t>
+          <t>-78.75524</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>223784</t>
+          <t>274976</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80832</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.6022</t>
+          <t>-8.4663</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.7216</t>
+          <t>-78.8684</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>274764</t>
+          <t>275042</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1588 MI MUNDO FELIZ</t>
+          <t>81700</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.42408</t>
+          <t>-8.40514</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.78323</t>
+          <t>-78.82339</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>716</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>274839</t>
+          <t>566017</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80070 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>SAGRADOS CORAZONES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.41654</t>
+          <t>-8.42159</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.75072</t>
+          <t>-78.77616</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>274858</t>
+          <t>690470</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80073 JOSE ABELARDO QUIÑONEZ GONZALES</t>
+          <t>ADVENTURE SCHOOL'S</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.3734</t>
+          <t>-8.42067</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.6543</t>
+          <t>-78.77187</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>274863</t>
+          <t>275339</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80074 MARIA CARIDAD AGUERO DE ARRESSE</t>
+          <t>81540</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.423504</t>
+          <t>-8.7464</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.781147</t>
+          <t>-78.5221</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>274877</t>
+          <t>657569</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.427537</t>
+          <t>-8.42394</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.83576</t>
+          <t>-78.77688</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>179</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>274900</t>
+          <t>274957</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80095 JOSE OLAYA</t>
+          <t>80704 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.44797</t>
+          <t>-8.3796</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.818405</t>
+          <t>-78.6795</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>274919</t>
+          <t>275141</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80096 FRANCISCO BOLOGNESI</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.4679</t>
+          <t>-8.412940000000003</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.8476</t>
+          <t>-78.7529</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>274938</t>
+          <t>701256</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>80702 MARIA SANDOVAL ROBLES</t>
+          <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.409059</t>
+          <t>-8.538320000000002</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.80837</t>
+          <t>-78.67471</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>462</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>274957</t>
+          <t>819185</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>80704 ANDRES AVELINO CACERES</t>
+          <t>MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.3796</t>
+          <t>-8.42456</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.6795</t>
+          <t>-78.77975</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>275042</t>
+          <t>274858</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>80073 JOSE ABELARDO QUIÑONEZ GONZALES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.40514</t>
+          <t>-8.3734</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.82339</t>
+          <t>-78.6543</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>275056</t>
+          <t>733672</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>81701</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.431685</t>
+          <t>-8.602</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.797331</t>
+          <t>-78.7218</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>275117</t>
+          <t>819251</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>80755</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.467280000000002</t>
+          <t>-8.41617</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.866609</t>
+          <t>-78.75837</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>275141</t>
+          <t>907417</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>GARDNER SCHOOL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.412940000000003</t>
+          <t>-8.418537000000002</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.7529</t>
+          <t>-78.765733</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>275278</t>
+          <t>274919</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>80635 SAN JUAN BAUTISTA</t>
+          <t>80096 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.48039</t>
+          <t>-8.4679</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.63298</t>
+          <t>-78.8476</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>371</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>275339</t>
+          <t>819190</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>81540</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.7464</t>
+          <t>-8.546137</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.5221</t>
+          <t>-78.677008</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>275363</t>
+          <t>274900</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>81770 MARIA INMACULADA CONCEPCION</t>
+          <t>80095 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.537135</t>
+          <t>-8.44797</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.671621</t>
+          <t>-78.818405</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>517319</t>
+          <t>659889</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GENERAL SIMON BOLIVAR</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.42276</t>
+          <t>-8.40305</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.77881</t>
+          <t>-78.82274</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>593</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>566017</t>
+          <t>275117</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAGRADOS CORAZONES</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.42159</t>
+          <t>-8.467280000000002</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.77616</t>
+          <t>-78.866609</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>493</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>636497</t>
+          <t>819171</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>CHRISTIAN BARNARD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.5382</t>
+          <t>-8.405150000000003</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.674</t>
+          <t>-78.82216</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>609</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>647009</t>
+          <t>223784</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>80832</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.40458</t>
+          <t>-8.6022</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.82329</t>
+          <t>-78.7216</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>656089</t>
+          <t>636497</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.4053</t>
+          <t>-8.5382</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.82128</t>
+          <t>-78.674</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>657569</t>
+          <t>775266</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.42394</t>
+          <t>-8.41129</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.77688</t>
+          <t>-78.81253</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,42 +2113,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>657913</t>
+          <t>791365</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INMACULADA VIRGEN DE LA PUERTA</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.41512</t>
+          <t>-8.43245</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.75524</t>
+          <t>-78.77129</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>659889</t>
+          <t>754607</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>COAR LA LIBERTAD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.40305</t>
+          <t>-8.410080000000002</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.82274</t>
+          <t>-78.7245</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>690470</t>
+          <t>274877</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ADVENTURE SCHOOL'S</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.42067</t>
+          <t>-8.427537</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.77187</t>
+          <t>-78.83576</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>566</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>701256</t>
+          <t>274938</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI</t>
+          <t>80702 MARIA SANDOVAL ROBLES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.538320000000002</t>
+          <t>-8.409059</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.67471</t>
+          <t>-78.80837</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>905</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>733672</t>
+          <t>517319</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>GENERAL SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.602</t>
+          <t>-8.42276</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.7218</t>
+          <t>-78.77881</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>754607</t>
+          <t>647009</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>COAR LA LIBERTAD</t>
+          <t>81700</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.410080000000002</t>
+          <t>-8.40458</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.7245</t>
+          <t>-78.82329</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>775266</t>
+          <t>275278</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>80635 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.41129</t>
+          <t>-8.48039</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.81253</t>
+          <t>-78.63298</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>931</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>791365</t>
+          <t>275056</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>81701</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.43245</t>
+          <t>-8.431685</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.77129</t>
+          <t>-78.797331</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>101</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>819171</t>
+          <t>80672</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CHRISTIAN BARNARD</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.405150000000003</t>
+          <t>-8.414277</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.82216</t>
+          <t>-78.752222</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>819185</t>
+          <t>274764</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MARIA DE FATIMA</t>
+          <t>1588 MI MUNDO FELIZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.42456</t>
+          <t>-8.42408</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.77975</t>
+          <t>-78.78323</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>819190</t>
+          <t>823724</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>82206 VALLE DE DIOS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.546137</t>
+          <t>-8.512575</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.677008</t>
+          <t>-78.680389</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>819251</t>
+          <t>275363</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>81770 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.41617</t>
+          <t>-8.537135</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.75837</t>
+          <t>-78.671621</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,42 +2857,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>823724</t>
+          <t>274839</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>82206 VALLE DE DIOS</t>
+          <t>80070 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.512575</t>
+          <t>-8.41654</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.680389</t>
+          <t>-78.75072</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>907417</t>
+          <t>656089</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GARDNER SCHOOL</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.418537000000002</t>
+          <t>-8.4053</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.765733</t>
+          <t>-78.82128</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>274976</t>
+          <t>274863</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80755</t>
+          <t>80074 MARIA CARIDAD AGUERO DE ARRESSE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.4663</t>
+          <t>-8.423504</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.8684</t>
+          <t>-78.781147</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.413790000000002</t>
+          <t>-8.41379</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.412940000000003</t>
+          <t>-8.41294</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.538320000000002</t>
+          <t>-8.53832</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.418537000000002</t>
+          <t>-8.418537</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.467280000000002</t>
+          <t>-8.46728</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.405150000000003</t>
+          <t>-8.40515</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.410080000000002</t>
+          <t>-8.41008</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>657913</t>
+          <t>907417</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>INMACULADA VIRGEN DE LA PUERTA</t>
+          <t>GARDNER SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.41512</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.75524</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.418537000000002</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-78.765733</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>274976</t>
+          <t>823724</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80755</t>
+          <t>82206 VALLE DE DIOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.4663</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.8684</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.512575</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-78.680389</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>274759</t>
+          <t>819251</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.41457</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.75069</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-8.41617</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.75837</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>275042</t>
+          <t>819190</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.40514</t>
+          <t>461</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.82339</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>-8.546137</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.677008</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>274820</t>
+          <t>819185</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIRU</t>
+          <t>MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.41379</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.75171</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>-8.42456</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-78.77975</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>566017</t>
+          <t>819171</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAGRADOS CORAZONES</t>
+          <t>CHRISTIAN BARNARD</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.42159</t>
+          <t>609</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.77616</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-8.405150000000003</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.82216</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>690470</t>
+          <t>791365</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ADVENTURE SCHOOL'S</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.42067</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.77187</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-8.43245</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.77129</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>275339</t>
+          <t>775266</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81540</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.7464</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.5221</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-8.41129</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.81253</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>657569</t>
+          <t>754607</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>COAR LA LIBERTAD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.42394</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.77688</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-8.410080000000002</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.7245</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>274957</t>
+          <t>733672</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80704 ANDRES AVELINO CACERES</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.3796</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.6795</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-8.602</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.7218</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>275141</t>
+          <t>701256</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.41294</t>
+          <t>462</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.7529</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-8.538320000000002</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.67471</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>701256</t>
+          <t>690470</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI</t>
+          <t>ADVENTURE SCHOOL'S</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.53832</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.67471</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>-8.42067</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.77187</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>819185</t>
+          <t>659889</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARIA DE FATIMA</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.42456</t>
+          <t>593</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.77975</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-8.40305</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.82274</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>274858</t>
+          <t>657913</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80073 JOSE ABELARDO QUIÑONEZ GONZALES</t>
+          <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.3734</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.6543</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-8.41512</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.75524</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>733672</t>
+          <t>657569</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.602</t>
+          <t>179</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.7218</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-8.42394</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-78.77688</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>819251</t>
+          <t>656089</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VIRGEN DE GUADALUPE</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.41617</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.75837</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>-8.4053</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.82128</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>907417</t>
+          <t>647009</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GARDNER SCHOOL</t>
+          <t>81700</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.418537</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.765733</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-8.40458</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.82329</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,42 +1555,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>274919</t>
+          <t>636497</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>80096 FRANCISCO BOLOGNESI</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.4679</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.8476</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>-8.5382</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.674</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>819190</t>
+          <t>566017</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>SAGRADOS CORAZONES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.546137</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.677008</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>-8.42159</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.77616</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,42 +1679,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>274900</t>
+          <t>517319</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80095 JOSE OLAYA</t>
+          <t>GENERAL SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.44797</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.818405</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>-8.42276</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.77881</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>659889</t>
+          <t>275363</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>81770 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.40305</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.82274</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>-8.537135</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.671621</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>275117</t>
+          <t>275339</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80755</t>
+          <t>81540</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.46728</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.866609</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>-8.7464</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.5221</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>819171</t>
+          <t>275278</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CHRISTIAN BARNARD</t>
+          <t>80635 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.40515</t>
+          <t>931</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.82216</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>-8.48039</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-78.63298</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>223784</t>
+          <t>275141</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>80832</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.6022</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.7216</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-8.412940000000003</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.7529</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>636497</t>
+          <t>275117</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.5382</t>
+          <t>493</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.674</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-8.467280000000002</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.866609</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>775266</t>
+          <t>275056</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>81701</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.41129</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.81253</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-8.431685</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.797331</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>791365</t>
+          <t>275042</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>81700</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.43245</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.77129</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-8.40514</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.82339</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>754607</t>
+          <t>274976</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COAR LA LIBERTAD</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.41008</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.7245</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-8.4663</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.8684</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,42 +2237,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>274877</t>
+          <t>274957</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>80704 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.427537</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.83576</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>-8.3796</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.6795</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>-8.409059</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-78.80837</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,42 +2361,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>517319</t>
+          <t>274919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GENERAL SIMON BOLIVAR</t>
+          <t>80096 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.42276</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.77881</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-8.4679</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-78.8476</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>647009</t>
+          <t>274900</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>80095 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.40458</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.82329</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>-8.44797</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-78.818405</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>275278</t>
+          <t>274877</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>80635 SAN JUAN BAUTISTA</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.48039</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.63298</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>-8.427537</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-78.83576</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>275056</t>
+          <t>274863</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>81701</t>
+          <t>80074 MARIA CARIDAD AGUERO DE ARRESSE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.431685</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.797331</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>-8.423504</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-78.781147</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>274858</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>80073 JOSE ABELARDO QUIÑONEZ GONZALES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.414277</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.752222</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-8.3734</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.6543</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>274764</t>
+          <t>274839</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1588 MI MUNDO FELIZ</t>
+          <t>80070 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.42408</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.78323</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>-8.41654</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.75072</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>823724</t>
+          <t>274820</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>82206 VALLE DE DIOS</t>
+          <t>VIRU</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.512575</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.680389</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>-8.413790000000002</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-78.75171</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>275363</t>
+          <t>274764</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>81770 MARIA INMACULADA CONCEPCION</t>
+          <t>1588 MI MUNDO FELIZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.537135</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.671621</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>-8.42408</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-78.78323</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>274839</t>
+          <t>274759</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>80070 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.41654</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.75072</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>-8.41457</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-78.75069</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>656089</t>
+          <t>223784</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>80832</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.4053</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.82128</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-8.6022</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.7216</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>274863</t>
+          <t>080672</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80074 MARIA CARIDAD AGUERO DE ARRESSE</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.423504</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.781147</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>-8.414277</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-78.752222</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-VIRU-VIRU.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
